--- a/sample_data/sample_data/sample_changes.xlsx
+++ b/sample_data/sample_data/sample_changes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,11 +477,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Complexity</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Long description</t>
         </is>
       </c>
     </row>
@@ -546,7 +541,6 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,7 +602,6 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -671,7 +664,6 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -733,7 +725,6 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -798,7 +789,6 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -860,7 +850,6 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -925,7 +914,6 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -989,7 +977,6 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1049,7 +1036,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1109,7 +1095,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1164,7 +1149,6 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1225,7 +1209,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1233,7 +1216,11 @@
           <t>Update production configuration file</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Some configuration updates needed in production</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>standard</t>
@@ -1272,11 +1259,6 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>medium</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Some configuration updates needed in production</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1315,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1393,7 +1374,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1452,7 +1432,6 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1513,7 +1492,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1573,7 +1551,6 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1633,7 +1610,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1692,7 +1668,6 @@
           <t>low</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1752,7 +1727,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1812,7 +1786,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1872,7 +1845,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1932,7 +1904,6 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
